--- a/Repository/Settings/RepositoryTranslations.xlsx
+++ b/Repository/Settings/RepositoryTranslations.xlsx
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8976,6 +8976,138 @@
       <c r="E365" t="inlineStr">
         <is>
           <t>Liste des produits, filtrée en cascade selon la catégorie sélectionnée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Reading {path}</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Lecture de {path}</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Searching the Seal examples for {regex}</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Recherche de {regex} dans les exemples Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Describing the class {name}</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Description de la classe {name}</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Listing the view templates</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Liste des modèles de vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Reading the parameters of the view template {template}</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Lecture des paramètres du modèle de vue {template}</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Modifying the report {path}</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Modification du rapport {path}</t>
         </is>
       </c>
     </row>

--- a/Repository/Settings/RepositoryTranslations.xlsx
+++ b/Repository/Settings/RepositoryTranslations.xlsx
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:E372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9108,6 +9108,28 @@
       <c r="E371" t="inlineStr">
         <is>
           <t>Modification du rapport {path}</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>AIToolProgress</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Checking the security</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Vérification de la sécurité</t>
         </is>
       </c>
     </row>
